--- a/datos/indicadores_adelantados/cemento/produccion_cemento_depto_1991_2026.xlsx
+++ b/datos/indicadores_adelantados/cemento/produccion_cemento_depto_1991_2026.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\3. IGAE\2026-08 Agosto\5. Cemento\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ljuanes\Desktop\Luz Angel JH\1. Cemento\7. RESULTADOS\4. IGAE hasta el 10 de cada mes\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10440" windowHeight="11010"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27360" windowHeight="8820"/>
   </bookViews>
   <sheets>
     <sheet name="C1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="26">
   <si>
     <t>Enero</t>
   </si>
@@ -792,7 +792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C1:S506"/>
+  <dimension ref="C1:S507"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="1.42578125" style="2" customWidth="1"/>
@@ -15770,7 +15770,7 @@
       <c r="R467" s="3"/>
       <c r="S467" s="3"/>
     </row>
-    <row r="468" spans="3:19" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="468" spans="3:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C468" s="20">
         <v>2024</v>
       </c>
@@ -16244,7 +16244,7 @@
       <c r="R481" s="3"/>
       <c r="S481" s="3"/>
     </row>
-    <row r="482" spans="3:19" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="482" spans="3:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C482" s="20">
         <v>2025</v>
       </c>
@@ -16723,25 +16723,32 @@
         <v>23</v>
       </c>
       <c r="D496" s="24">
-        <v>325114.33999999997</v>
+        <f>SUM(D497:D503)</f>
+        <v>397703.72</v>
       </c>
       <c r="E496" s="24">
-        <v>314127.57000000007</v>
+        <f t="shared" ref="E496:J496" si="0">SUM(E497:E503)</f>
+        <v>390697.56000000006</v>
       </c>
       <c r="F496" s="24">
-        <v>243298</v>
+        <f t="shared" si="0"/>
+        <v>312419</v>
       </c>
       <c r="G496" s="24">
-        <v>84216.11</v>
+        <f t="shared" si="0"/>
+        <v>90572.17</v>
       </c>
       <c r="H496" s="24">
-        <v>75659.16</v>
+        <f t="shared" si="0"/>
+        <v>88191.360000000001</v>
       </c>
       <c r="I496" s="24">
-        <v>461215.91</v>
+        <f t="shared" si="0"/>
+        <v>558426.03899999999</v>
       </c>
       <c r="J496" s="24">
-        <v>1503631.09</v>
+        <f t="shared" si="0"/>
+        <v>1838009.8489999999</v>
       </c>
       <c r="K496" s="6"/>
       <c r="L496" s="3"/>
@@ -16964,14 +16971,30 @@
       <c r="S502" s="3"/>
     </row>
     <row r="503" spans="3:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="C503" s="22"/>
-      <c r="D503" s="25"/>
-      <c r="E503" s="25"/>
-      <c r="F503" s="25"/>
-      <c r="G503" s="25"/>
-      <c r="H503" s="25"/>
-      <c r="I503" s="25"/>
-      <c r="J503" s="25"/>
+      <c r="C503" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="D503" s="28">
+        <v>72589.37999999999</v>
+      </c>
+      <c r="E503" s="28">
+        <v>76569.989999999976</v>
+      </c>
+      <c r="F503" s="28">
+        <v>69121</v>
+      </c>
+      <c r="G503" s="28">
+        <v>6356.06</v>
+      </c>
+      <c r="H503" s="28">
+        <v>12532.2</v>
+      </c>
+      <c r="I503" s="28">
+        <v>97210.128999999986</v>
+      </c>
+      <c r="J503" s="28">
+        <v>334378.75899999996</v>
+      </c>
       <c r="K503" s="6"/>
       <c r="L503" s="3"/>
       <c r="M503" s="3"/>
@@ -16983,31 +17006,50 @@
       <c r="S503" s="3"/>
     </row>
     <row r="504" spans="3:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="C504" s="9" t="s">
+      <c r="C504" s="22"/>
+      <c r="D504" s="25"/>
+      <c r="E504" s="25"/>
+      <c r="F504" s="25"/>
+      <c r="G504" s="25"/>
+      <c r="H504" s="25"/>
+      <c r="I504" s="25"/>
+      <c r="J504" s="25"/>
+      <c r="K504" s="6"/>
+      <c r="L504" s="3"/>
+      <c r="M504" s="3"/>
+      <c r="N504" s="3"/>
+      <c r="O504" s="3"/>
+      <c r="P504" s="3"/>
+      <c r="Q504" s="3"/>
+      <c r="R504" s="3"/>
+      <c r="S504" s="3"/>
+    </row>
+    <row r="505" spans="3:19" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C505" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D504" s="2"/>
-      <c r="E504" s="2"/>
-      <c r="F504" s="2"/>
-      <c r="G504" s="2"/>
-      <c r="H504" s="2"/>
-      <c r="J504" s="2"/>
-    </row>
-    <row r="505" spans="3:19" x14ac:dyDescent="0.2">
-      <c r="C505" s="9" t="s">
+      <c r="D505" s="2"/>
+      <c r="E505" s="2"/>
+      <c r="F505" s="2"/>
+      <c r="G505" s="2"/>
+      <c r="H505" s="2"/>
+      <c r="J505" s="2"/>
+    </row>
+    <row r="506" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C506" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I505" s="4"/>
-    </row>
-    <row r="506" spans="3:19" x14ac:dyDescent="0.2">
-      <c r="C506" s="9"/>
-      <c r="D506" s="27"/>
-      <c r="E506" s="27"/>
-      <c r="F506" s="27"/>
-      <c r="G506" s="27"/>
-      <c r="H506" s="27"/>
-      <c r="I506" s="27"/>
-      <c r="J506" s="27"/>
+      <c r="I506" s="4"/>
+    </row>
+    <row r="507" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C507" s="9"/>
+      <c r="D507" s="27"/>
+      <c r="E507" s="27"/>
+      <c r="F507" s="27"/>
+      <c r="G507" s="27"/>
+      <c r="H507" s="27"/>
+      <c r="I507" s="27"/>
+      <c r="J507" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datos/indicadores_adelantados/cemento/produccion_cemento_depto_1991_2026.xlsx
+++ b/datos/indicadores_adelantados/cemento/produccion_cemento_depto_1991_2026.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ljuanes\Desktop\Luz Angel JH\1. Cemento\7. RESULTADOS\4. IGAE hasta el 10 de cada mes\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ljuanes\Desktop\Luz Angel JH\1. Cemento\7. RESULTADOS\4. IGAE hasta el 10 de cada mes\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27360" windowHeight="8820"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14790" windowHeight="10485"/>
   </bookViews>
   <sheets>
     <sheet name="C1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="26">
   <si>
     <t>Enero</t>
   </si>
@@ -792,7 +792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C1:S507"/>
+  <dimension ref="C1:S508"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="1.42578125" style="2" customWidth="1"/>
@@ -16723,32 +16723,32 @@
         <v>23</v>
       </c>
       <c r="D496" s="24">
-        <f>SUM(D497:D503)</f>
-        <v>397703.72</v>
+        <f>SUM(D497:D504)</f>
+        <v>473672.37</v>
       </c>
       <c r="E496" s="24">
-        <f t="shared" ref="E496:J496" si="0">SUM(E497:E503)</f>
-        <v>390697.56000000006</v>
+        <f t="shared" ref="E496:J496" si="0">SUM(E497:E504)</f>
+        <v>457088.47000000003</v>
       </c>
       <c r="F496" s="24">
         <f t="shared" si="0"/>
-        <v>312419</v>
+        <v>370219</v>
       </c>
       <c r="G496" s="24">
         <f t="shared" si="0"/>
-        <v>90572.17</v>
+        <v>95323.28</v>
       </c>
       <c r="H496" s="24">
         <f t="shared" si="0"/>
-        <v>88191.360000000001</v>
+        <v>103741.26</v>
       </c>
       <c r="I496" s="24">
         <f t="shared" si="0"/>
-        <v>558426.03899999999</v>
+        <v>627768.71699999995</v>
       </c>
       <c r="J496" s="24">
         <f t="shared" si="0"/>
-        <v>1838009.8489999999</v>
+        <v>2127813.0970000001</v>
       </c>
       <c r="K496" s="6"/>
       <c r="L496" s="3"/>
@@ -17006,14 +17006,30 @@
       <c r="S503" s="3"/>
     </row>
     <row r="504" spans="3:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="C504" s="22"/>
-      <c r="D504" s="25"/>
-      <c r="E504" s="25"/>
-      <c r="F504" s="25"/>
-      <c r="G504" s="25"/>
-      <c r="H504" s="25"/>
-      <c r="I504" s="25"/>
-      <c r="J504" s="25"/>
+      <c r="C504" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D504" s="28">
+        <v>75968.649999999994</v>
+      </c>
+      <c r="E504" s="28">
+        <v>66390.909999999989</v>
+      </c>
+      <c r="F504" s="28">
+        <v>57800</v>
+      </c>
+      <c r="G504" s="28">
+        <v>4751.1099999999997</v>
+      </c>
+      <c r="H504" s="28">
+        <v>15549.9</v>
+      </c>
+      <c r="I504" s="28">
+        <v>69342.678</v>
+      </c>
+      <c r="J504" s="28">
+        <v>289803.24799999996</v>
+      </c>
       <c r="K504" s="6"/>
       <c r="L504" s="3"/>
       <c r="M504" s="3"/>
@@ -17025,31 +17041,50 @@
       <c r="S504" s="3"/>
     </row>
     <row r="505" spans="3:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="C505" s="9" t="s">
+      <c r="C505" s="22"/>
+      <c r="D505" s="25"/>
+      <c r="E505" s="25"/>
+      <c r="F505" s="25"/>
+      <c r="G505" s="25"/>
+      <c r="H505" s="25"/>
+      <c r="I505" s="25"/>
+      <c r="J505" s="25"/>
+      <c r="K505" s="6"/>
+      <c r="L505" s="3"/>
+      <c r="M505" s="3"/>
+      <c r="N505" s="3"/>
+      <c r="O505" s="3"/>
+      <c r="P505" s="3"/>
+      <c r="Q505" s="3"/>
+      <c r="R505" s="3"/>
+      <c r="S505" s="3"/>
+    </row>
+    <row r="506" spans="3:19" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="C506" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D505" s="2"/>
-      <c r="E505" s="2"/>
-      <c r="F505" s="2"/>
-      <c r="G505" s="2"/>
-      <c r="H505" s="2"/>
-      <c r="J505" s="2"/>
-    </row>
-    <row r="506" spans="3:19" x14ac:dyDescent="0.2">
-      <c r="C506" s="9" t="s">
+      <c r="D506" s="2"/>
+      <c r="E506" s="2"/>
+      <c r="F506" s="2"/>
+      <c r="G506" s="2"/>
+      <c r="H506" s="2"/>
+      <c r="J506" s="2"/>
+    </row>
+    <row r="507" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C507" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I506" s="4"/>
-    </row>
-    <row r="507" spans="3:19" x14ac:dyDescent="0.2">
-      <c r="C507" s="9"/>
-      <c r="D507" s="27"/>
-      <c r="E507" s="27"/>
-      <c r="F507" s="27"/>
-      <c r="G507" s="27"/>
-      <c r="H507" s="27"/>
-      <c r="I507" s="27"/>
-      <c r="J507" s="27"/>
+      <c r="I507" s="4"/>
+    </row>
+    <row r="508" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C508" s="9"/>
+      <c r="D508" s="27"/>
+      <c r="E508" s="27"/>
+      <c r="F508" s="27"/>
+      <c r="G508" s="27"/>
+      <c r="H508" s="27"/>
+      <c r="I508" s="27"/>
+      <c r="J508" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
